--- a/apps/web/public/downloads/temt-sample-report.xlsx
+++ b/apps/web/public/downloads/temt-sample-report.xlsx
@@ -15641,7 +15641,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43961080-B250-4593-BF23-F3C1F3785D9B}</x14:id>
+          <x14:id>{7BA921D6-3EBE-4939-93C1-25AA04EDE716}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -15652,7 +15652,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43961080-B250-4593-BF23-F3C1F3785D9B}">
+          <x14:cfRule type="dataBar" id="{7BA921D6-3EBE-4939-93C1-25AA04EDE716}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
